--- a/FIRE_Navigator_Kunal_2026.xlsx
+++ b/FIRE_Navigator_Kunal_2026.xlsx
@@ -482,7 +482,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>{"meta":{"onboardingComplete":true,"createdAt":1782750733361,"lastSaved":1788762816564,"currentTab":"reports","_subtab":"budget","_draftLogMonth":"2026-08","_draftLogAmounts":[18600,10598,4500,23000,2065,9600,6400,389,9120,11723,2700,10188,11000,7276,6741,1477,804,5804,1150,900,3000,0,9390,6600],"_topupDraftAmount":[0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0],"_topupDraftNote":["","","","","","","","","","","","","","","","","","","","","","","","",""],"_inflBudgetYear":2026,"budgetBaseYear":2025},"expenseLog":[{"id":"log_01p0s0z","month":"2026-06","entries":{"Domestic Help (Cleaner+Maintenance)":13100,"Groceries":11700,"Cook":2133,"Nanny / Childcare":23000,"Insurance":2065,"Vape":8300,"Shopping":7000,"Gas Bill &amp; Utilities":0,"Vaccination":0,"Fuel &amp; Transport":12000,"Repairs":3850,"AI Project / Side projects":2232,"Baby Expenses":6500,"Eating Out / Movies":7631,"Gifts":3400,"Subscriptions (Netflix/Prime)":830,"Protein / Supplements":526,"Health":1820,"Grooming":50,"Travel":12380,"Maid":880,"Capital Replacement":0,"Child Experiences":0,"Home Refreshes/Interiors":0},"total":119397,"loggedAt":1782836277573},{"id":"log_zh4odkq","month":"2026-07","entries":{"Domestic Help (Cleaner+Maintenance)":9870,"Groceries":13984,"Cook":4500,"Nanny / Childcare":23000,"Insurance":2085,"Vape":8300,"Shopping":10867,"Gas Bill &amp; Utilities":675,"Vaccination":0,"Fuel &amp; Transport":9977,"Repairs":2600,"AI Project / Side projects":1840,"Baby Expenses":4797,"Eating Out / Movies":7689,"Gifts":2082,"Subscriptions (Netflix/Prime)":1477,"Protein / Supplements":804,"Health":1247,"Grooming":2120,"Travel":0,"Maid":3000,"Capital Replacement":8350,"Child Experiences":15046,"Home Refreshes/Interiors":0},"total":134310,"loggedAt":1787548574814},{"id":"log_h5v9azb","month":"2026-08","entries":{"Domestic Help (Cleaner+Maintenance)":18600,"Groceries":10598,"Cook":4500,"Nanny / Childcare":23000,"Insurance":2065,"Vape":9600,"Shopping":6400,"Gas Bill &amp; Utilities":389,"Vaccination":9120,"Fuel &amp; Transport":11723,"Repairs":2700,"AI Project / Side projects":10188,"Baby Expenses":11000,"Eating Out / Movies":7276,"Gifts":6741,"Subscriptions (Netflix/Prime)":1477,"Protein / Supplements":804,"Health":5804,"Grooming":1150,"Travel":900,"Maid":3000,"Capital Replacement":0,"Child Experiences":9390,"Home Refreshes/Interiors":6600},"total":163025,"loggedAt":1788359648795}],"profile":{"userName":"Kunal","spouseName":"Madhu","hasSpouse":true,"userAge":34,"spouseAge":35,"retirementAge":44,"lifeExpectancy":85,"children":[{"name":"Rahee","age":1}]},"inflation":{"general":0.08,"food":0.08,"education":0.1,"healthcare":0.12,"lifestyle":0.08},"returns":{"equity":0.12,"debt":0.07,"gold":0.08,"realestate":0.08,"epf":0.08,"cash":0.035},"risk":{"emergencyMonths":9,"healthReserve":500000,"bufferPct":0.05,"ltcReserve":1500000},"income":{"userMonthly":310000,"spouseMonthly":230000,"annualBonus":762000,"rsu":0,"otherIncome":0,"userGrowth":0.08,"spouseGrowth":0.08,"promotionJumpPct":0.15,"promotionEveryYears":4,"careerBreak":{"enabled":false,"startAge":36,"durationYears":1,"incomeReplacementPct":0}},"assets":[{"id":"a1","name":"Mutual Funds","owner":"Kunal","cls":"equity","balance":5832888,"monthlyContribution":86000,"stepUpPct":0.08},{"id":"a2","name":"Groww","owner":"Kunal","cls":"equity","balance":243498,"monthlyContribution":1500,"stepUpPct":0},{"id":"a3","name":"Amazon Stocks (RSU)","owner":"Kunal","cls":"equity","balance":2111263,"monthlyContribution":0,"stepUpPct":0},{"id":"a4","name":"EPFO","owner":"Kunal","cls":"epf","balance":1447167,"monthlyContribution":10800,"stepUpPct":0.08},{"id":"a5","name":"Savings","owner":"Kunal","cls":"cash","balance":160626,"monthlyContribution":0,"stepUpPct":0},{"id":"a6","name":"Fixed Deposit","owner":"Kunal","cls":"debt","balance":281593,"monthlyContribution":0,"stepUpPct":0},{"id":"a7","name":"ULIP","owner":"Kunal","cls":"debt","balance":99701,"monthlyContribution":10000,"stepUpPct":0},{"id":"a8","name":"US Stocks","owner":"Kunal","cls":"equity","balance":272792,"monthlyContribution":35000,"stepUpPct":0.08},{"id":"a9","name":"NPS","owner":"Kunal","cls":"epf","balance":319285,"monthlyContribution":5000,"stepUpPct":0},{"id":"a10","name":"Mutual Funds","owner":"Madhu","cls":"equity","balance":5795352,"monthlyContribution":119958,"stepUpPct":0.08},{"id":"a11","name":"Savings","owner":"Madhu","cls":"cash","balance":1094070,"monthlyContribution":0,"stepUpPct":0},{"id":"a12","name":"Fixed Deposit","owner":"Madhu","cls":"debt","balance":1081910,"monthlyContribution":0,"stepUpPct":0},{"id":"a13","name":"EPFO","owner":"Madhu","cls":"epf","balance":1743743,"monthlyContribution":10800,"stepUpPct":0.08},{"id":"a14","name":"Stocks","owner":"Madhu","cls":"equity","balance":399053,"monthlyContribution":11000,"stepUpPct":0},{"id":"a15","name":"NPS","owner":"Madhu","cls":"epf","balance":394323,"monthlyContribution":5000,"stepUpPct":0},{"id":"a16","name":"Gold","owner":"Madhu","cls":"gold","balance":153010,"monthlyContribution":0,"stepUpPct":0}],"liabilities":{"homeLoan":{"enabled":true,"principal":5300000,"rate":0.072,"tenureYears":24,"emi":38000},"personalLoan":{"enabled":false,"principal":0,"rate":0.12,"tenureYears":0,"emi":0},"vehicleLoan":{"enabled":false,"principal":0,"rate":0.09,"tenureYears":0,"emi":0},"otherDebt":{"enabled":false,"principal":0,"rate":0.1,"tenureYears":0,"emi":0},"prepayment":{"annualAmount":700000,"annualGrowthPct":0}},"expenses":[{"name":"Home Loan EMI","amount":38000,"group":"Survival","linkedToLoan":true,"inflationType":"general"},{"name":"Domestic Help (Cleaner+Maintenance)","amount":9600,"group":"Survival","inflationType":"general"},{"name":"Groceries","amount":14000,"group":"Survival","inflationType":"food","isBucket":true,"annualBudget":168000},{"name":"Cook","amount":4500,"group":"Survival","inflationType":"general"},{"name":"Nanny / Childcare","amount":23000,"group":"Survival","inflationType":"general"},{"name":"Insurance","amount":4000,"group":"Discretionary","inflationType":"general"},{"name":"Vape","amount":8000,"group":"Discretionary","inflationType":"lifestyle","isBucket":true,"annualBudget":96000},{"name":"Shopping","amount":9000,"group":"Discretionary","inflationType":"lifestyle","isBucket":true,"annualBudget":108000},{"name":"Gas Bill &amp; Utilities","amount":540,"group":"Survival","inflationType":"general"},{"name":"Vaccination","amount":3000,"group":"Survival","inflationType":"healthcare","isBucket":true,"annualBudget":36000},{"name":"Fuel &amp; Transport","amount":7000,"group":"Survival","inflationType":"general"},{"name":"Repairs","amount":5000,"group":"Survival","inflationType":"general","isBucket":true,"annualBudget":60000},{"name":"AI Project / Side projects","amount":3000,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Baby Expenses","amount":3000,"group":"Survival","inflationType":"healthcare"},{"name":"Eating Out / Movies","amount":8000,"group":"Discretionary","inflationType":"lifestyle","isBucket":true,"annualBudget":96000},{"name":"Gifts","amount":3000,"group":"Discretionary","inflationType":"lifestyle","isBucket":true,"annualBudget":36000},{"name":"Subscriptions (Netflix/Prime)","amount":1477,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Protein / Supplements","amount":1400,"group":"Survival","inflationType":"healthcare"},{"name":"Health","amount":1500,"group":"Survival","inflationType":"healthcare"},{"name":"Grooming","amount":4000,"group":"Survival","inflationType":"lifestyle","isBucket":true,"annualBudget":48000},{"name":"Travel","amount":30000,"group":"Discretionary","inflationType":"lifestyle","isBucket":true,"annualBudget":360000,"topUps":[{"id":"topup_t1874gn","amount":100000,"note":"Annual Performance Bonus","date":"2026-08-24"}]},{"name":"Maid","amount":3000,"group":"Survival"},{"name":"Capital Replacement","amount":10000,"group":"Survival","inflationType":"lifestyle","isBucket":true,"annualBudget":120000},{"name":"Child Experiences","amount":11000,"group":"Discretionary","inflationType":"lifestyle","isBucket":true,"annualBudget":132000},{"name":"Home Refreshes/Interiors","amount":5000,"group":"Discretionary","inflationType":"lifestyle","isBucket":true,"annualBudget":60000}],"goals":[{"id":"g1","type":"education","name":"Child 1 — Foreign Masters","childIndex":0,"targetAge":23,"costToday":7000000,"inflation":0.09},{"id":"g2","type":"marriage","name":"Child 1 — Marriage","childIndex":0,"targetAge":28,"costToday":2500000,"inflation":0.07},{"id":"g4","type":"car","name":"Car Replacement","recurring":true,"frequencyYears":7,"costToday":1200000,"inflation":0.06,"startYear":2029}],"fire":{"type":"comfortable","retirementSpendPct":1,"postRetMonthlySpendToday":136050,"swr":0.03,"sequence":"neutral","fatMultiplier":1.5},"scenarios":[{"id":"sc_z49l70n","name":"Retire at 45 at 3% SWR","snapshot":{"profile":{"userName":"Kunal","spouseName":"Madhu","hasSpouse":true,"userAge":34,"spouseAge":35,"retirementAge":45,"lifeExpectancy":85,"children":[{"name":"Child 1","age":1}]},"income":{"userMonthly":200000,"spouseMonthly":200000,"annualBonus":950000,"rsu":0,"otherIncome":0,"userGrowth":0.08,"spouseGrowth":0.08,"promotionJumpPct":0.15,"promotionEveryYears":4,"careerBreak":{"enabled":false,"startAge":36,"durationYears":1,"incomeReplacementPct":0}},"assets":[{"id":"a1","name":"Mutual Funds","owner":"Kunal","cls":"equity","balance":5424000,"monthlyContribution":90000,"stepUpPct":0.08},{"id":"a2","name":"Groww","owner":"Kunal","cls":"equity","balance":245454,"monthlyContribution":5000,"stepUpPct":0.08},{"id":"a3","name":"Amazon Stocks (RSU)","owner":"Kunal","cls":"equity","balance":1868996,"monthlyContribution":0,"stepUpPct":0},{"id":"a4","name":"EPFO","owner":"Kunal","cls":"epf","balance":1423493,"monthlyContribution":18000,"stepUpPct":0.08},{"id":"a5","name":"Savings","owner":"Kunal","cls":"cash","balance":83552,"monthlyContribution":0,"stepUpPct":0},{"id":"a6","name":"Fixed Deposit","owner":"Kunal","cls":"debt","balance":281593,"monthlyContribution":0,"stepUpPct":0},{"id":"a7","name":"ULIP","owner":"Kunal","cls":"debt","balance":77196,"monthlyContribution":2000,"stepUpPct":0},{"id":"a8","name":"US Stocks","owner":"Kunal","cls":"equity","balance":208176,"monthlyContribution":10000,"stepUpPct":0.08},{"id":"a9","name":"NPS","owner":"Kunal","cls":"epf","balance":298189,"monthlyContribution":5000,"stepUpPct":0.08},{"id":"a10","name":"Mutual Funds","owner":"Madhu","cls":"equity","balance":5336945,"monthlyContribution":110000,"stepUpPct":0.08},{"id":"a11","name":"Savings","owner":"Madhu","cls":"cash","balance":1193087,"monthlyContribution":0,"stepUpPct":0},{"id":"a12","name":"Fixed Deposit","owner":"Madhu","cls":"debt","balance":1083873,"monthlyContribution":0,"stepUpPct":0},{"id":"a13","name":"EPFO","owner":"Madhu","cls":"epf","balance":1743743,"monthlyContribution":16000,"stepUpPct":0.08},{"id":"a14","name":"Stocks","owner":"Madhu","cls":"equity","balance":368384,"monthlyContribution":5054.5,"stepUpPct":0.08},{"id":"a15","name":"NPS","owner":"Madhu","cls":"epf","balance":368690,"monthlyContribution":5000,"stepUpPct":0.08},{"id":"a16","name":"Gold","owner":"Madhu","cls":"gold","balance":155910,"monthlyContribution":0,"stepUpPct":0}],"liabilities":{"homeLoan":{"enabled":true,"principal":6000000,"rate":0.072,"tenureYears":25,"emi":38000},"personalLoan":{"enabled":false,"principal":0,"rate":0.12,"tenureYears":0,"emi":0},"vehicleLoan":{"enabled":false,"principal":0,"rate":0.09,"tenureYears":0,"emi":0},"otherDebt":{"enabled":false,"principal":0,"rate":0.1,"tenureYears":0,"emi":0},"prepayment":{"annualAmount":700000,"annualGrowthPct":0.08}},"expenses":[{"name":"Home Loan EMI","amount":38000,"group":"Survival","linkedToLoan":true,"inflationType":"general"},{"name":"Domestic Help (Cleaner+Maintenance)","amount":9700,"group":"Survival","inflationType":"general"},{"name":"Groceries","amount":13800,"group":"Survival","inflationType":"food"},{"name":"Cook","amount":3300,"group":"Survival","inflationType":"food"},{"name":"Nanny / Childcare","amount":16300,"group":"Survival","inflationType":"general"},{"name":"Insurance","amount":3600,"group":"Discretionary","inflationType":"general"},{"name":"Vape","amount":7050,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Shopping","amount":7580,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Gas Bill &amp; Utilities","amount":540,"group":"Survival","inflationType":"general"},{"name":"Vaccination","amount":2850,"group":"Survival","inflationType":"healthcare"},{"name":"Fuel &amp; Transport","amount":4980,"group":"Survival","inflationType":"general"},{"name":"Repairs","amount":3660,"group":"Survival","inflationType":"general"},{"name":"AI Project / Side projects","amount":2490,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Baby Expenses","amount":5670,"group":"Survival","inflationType":"healthcare"},{"name":"Eating Out / Movies","amount":7920,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Gifts","amount":2640,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Subscriptions (Netflix/Prime)","amount":830,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Protein / Supplements","amount":960,"group":"Survival","inflationType":"healthcare"},{"name":"Health","amount":1270,"group":"Survival","inflationType":"healthcare"},{"name":"Grooming","amount":3240,"group":"Survival","inflationType":"lifestyle"},{"name":"Travel","amount":15280,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Maid","amount":3000,"group":"Survival"},{"name":"Capital Replacement","amount":10000,"group":"Survival","inflationType":"lifestyle"},{"name":"Child Experiences","amount":5000,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Home Refreshes/Interiors","amount":5000,"group":"Discretionary","inflationType":"lifestyle"}],"goals":[{"id":"g1","type":"education","name":"Child 1 — Foreign Masters","childIndex":0,"targetAge":23,"costToday":7000000,"inflation":0.09},{"id":"g2","type":"marriage","name":"Child 1 — Marriage","childIndex":0,"targetAge":28,"costToday":2500000,"inflation":0.07},{"id":"g4","type":"car","name":"Car Replacement","recurring":true,"frequencyYears":7,"costToday":1200000,"inflation":0.06,"startYear":2029}],"fire":{"type":"comfortable","retirementSpendPct":1,"postRetMonthlySpendToday":136050,"swr":0.03,"sequence":"neutral","fatMultiplier":1.5},"returns":{"equity":0.12,"debt":0.07,"gold":0.08,"realestate":0.08,"epf":0.08,"cash":0.035},"inflation":{"general":0.07,"food":0.07,"education":0.1,"healthcare":0.12,"lifestyle":0.08},"risk":{"emergencyMonths":9,"healthReserve":500000,"bufferPct":0.05,"ltcReserve":1500000}},"createdAt":1782751893034},{"id":"sc_pzn9rzn","name":"Retire at 44 at 3% SWR","snapshot":{"profile":{"userName":"Kunal","spouseName":"Madhu","hasSpouse":true,"userAge":34,"spouseAge":35,"retirementAge":44,"lifeExpectancy":85,"children":[{"name":"Child 1","age":1}]},"income":{"userMonthly":200000,"spouseMonthly":200000,"annualBonus":950000,"rsu":0,"otherIncome":0,"userGrowth":0.08,"spouseGrowth":0.08,"promotionJumpPct":0.15,"promotionEveryYears":4,"careerBreak":{"enabled":false,"startAge":36,"durationYears":1,"incomeReplacementPct":0}},"assets":[{"id":"a1","name":"Mutual Funds","owner":"Kunal","cls":"equity","balance":5424000,"monthlyContribution":90000,"stepUpPct":0.08},{"id":"a2","name":"Groww","owner":"Kunal","cls":"equity","balance":245454,"monthlyContribution":5000,"stepUpPct":0.08},{"id":"a3","name":"Amazon Stocks (RSU)","owner":"Kunal","cls":"equity","balance":1868996,"monthlyContribution":0,"stepUpPct":0},{"id":"a4","name":"EPFO","owner":"Kunal","cls":"epf","balance":1423493,"monthlyContribution":18000,"stepUpPct":0.08},{"id":"a5","name":"Savings","owner":"Kunal","cls":"cash","balance":83552,"monthlyContribution":0,"stepUpPct":0},{"id":"a6","name":"Fixed Deposit","owner":"Kunal","cls":"debt","balance":281593,"monthlyContribution":0,"stepUpPct":0},{"id":"a7","name":"ULIP","owner":"Kunal","cls":"debt","balance":77196,"monthlyContribution":2000,"stepUpPct":0},{"id":"a8","name":"US Stocks","owner":"Kunal","cls":"equity","balance":208176,"monthlyContribution":10000,"stepUpPct":0.08},{"id":"a9","name":"NPS","owner":"Kunal","cls":"epf","balance":298189,"monthlyContribution":5000,"stepUpPct":0.08},{"id":"a10","name":"Mutual Funds","owner":"Madhu","cls":"equity","balance":5336945,"monthlyContribution":110000,"stepUpPct":0.08},{"id":"a11","name":"Savings","owner":"Madhu","cls":"cash","balance":1193087,"monthlyContribution":0,"stepUpPct":0},{"id":"a12","name":"Fixed Deposit","owner":"Madhu","cls":"debt","balance":1083873,"monthlyContribution":0,"stepUpPct":0},{"id":"a13","name":"EPFO","owner":"Madhu","cls":"epf","balance":1743743,"monthlyContribution":16000,"stepUpPct":0.08},{"id":"a14","name":"Stocks","owner":"Madhu","cls":"equity","balance":368384,"monthlyContribution":5054.5,"stepUpPct":0.08},{"id":"a15","name":"NPS","owner":"Madhu","cls":"epf","balance":368690,"monthlyContribution":5000,"stepUpPct":0.08},{"id":"a16","name":"Gold","owner":"Madhu","cls":"gold","balance":155910,"monthlyContribution":0,"stepUpPct":0}],"liabilities":{"homeLoan":{"enabled":true,"principal":6000000,"rate":0.072,"tenureYears":25,"emi":38000},"personalLoan":{"enabled":false,"principal":0,"rate":0.12,"tenureYears":0,"emi":0},"vehicleLoan":{"enabled":false,"principal":0,"rate":0.09,"tenureYears":0,"emi":0},"otherDebt":{"enabled":false,"principal":0,"rate":0.1,"tenureYears":0,"emi":0},"prepayment":{"annualAmount":700000,"annualGrowthPct":0.08}},"expenses":[{"name":"Home Loan EMI","amount":38000,"group":"Survival","linkedToLoan":true,"inflationType":"general"},{"name":"Domestic Help (Cleaner+Maintenance)","amount":9700,"group":"Survival","inflationType":"general"},{"name":"Groceries","amount":13800,"group":"Survival","inflationType":"food"},{"name":"Cook","amount":3300,"group":"Survival","inflationType":"food"},{"name":"Nanny / Childcare","amount":16300,"group":"Survival","inflationType":"general"},{"name":"Insurance","amount":3600,"group":"Discretionary","inflationType":"general"},{"name":"Vape","amount":7050,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Shopping","amount":7580,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Gas Bill &amp; Utilities","amount":540,"group":"Survival","inflationType":"general"},{"name":"Vaccination","amount":2850,"group":"Survival","inflationType":"healthcare"},{"name":"Fuel &amp; Transport","amount":4980,"group":"Survival","inflationType":"general"},{"name":"Repairs","amount":3660,"group":"Survival","inflationType":"general"},{"name":"AI Project / Side projects","amount":2490,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Baby Expenses","amount":5670,"group":"Survival","inflationType":"healthcare"},{"name":"Eating Out / Movies","amount":7920,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Gifts","amount":2640,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Subscriptions (Netflix/Prime)","amount":830,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Protein / Supplements","amount":960,"group":"Survival","inflationType":"healthcare"},{"name":"Health","amount":1270,"group":"Survival","inflationType":"healthcare"},{"name":"Grooming","amount":3240,"group":"Survival","inflationType":"lifestyle"},{"name":"Travel","amount":15280,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Maid","amount":3000,"group":"Survival"},{"name":"Capital Replacement","amount":10000,"group":"Survival","inflationType":"lifestyle"},{"name":"Child Experiences","amount":5000,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Home Refreshes/Interiors","amount":5000,"group":"Discretionary","inflationType":"lifestyle"}],"goals":[{"id":"g1","type":"education","name":"Child 1 — Foreign Masters","childIndex":0,"targetAge":23,"costToday":7000000,"inflation":0.09},{"id":"g2","type":"marriage","name":"Child 1 — Marriage","childIndex":0,"targetAge":28,"costToday":2500000,"inflation":0.07},{"id":"g4","type":"car","name":"Car Replacement","recurring":true,"frequencyYears":7,"costToday":1200000,"inflation":0.06,"startYear":2029}],"fire":{"type":"comfortable","retirementSpendPct":1,"postRetMonthlySpendToday":136050,"swr":0.03,"sequence":"neutral","fatMultiplier":1.5},"returns":{"equity":0.12,"debt":0.07,"gold":0.08,"realestate":0.08,"epf":0.08,"cash":0.035},"inflation":{"general":0.07,"food":0.07,"education":0.1,"healthcare":0.12,"lifestyle":0.08},"risk":{"emergencyMonths":9,"healthReserve":500000,"bufferPct":0.05,"ltcReserve":1500000}},"createdAt":1782751922830}],"badges":{}}</v>
+        <v>{"meta":{"onboardingComplete":true,"createdAt":1782750733361,"lastSaved":1788934127555,"currentTab":"reports","_subtab":"budget","_draftLogMonth":"2026-08","_draftLogAmounts":[18600,10598,4500,23000,2065,9600,6400,389,9120,11723,2700,10188,11000,7276,6741,1477,804,5804,1150,900,3000,0,9390,6600],"_topupDraftAmount":[0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0],"_topupDraftNote":["","","","","","","","","","","","","","","","","","","","","","","","",""],"_inflBudgetYear":2026,"budgetBaseYear":2025},"expenseLog":[{"id":"log_01p0s0z","month":"2026-06","entries":{"Domestic Help (Cleaner+Maintenance)":13100,"Groceries":11700,"Cook":2133,"Nanny / Childcare":23000,"Insurance":2065,"Vape":8300,"Shopping":7000,"Gas Bill &amp; Utilities":0,"Vaccination":0,"Fuel &amp; Transport":12000,"Repairs":3850,"AI Project / Side projects":2232,"Baby Expenses":6500,"Eating Out / Movies":7631,"Gifts":3400,"Subscriptions (Netflix/Prime)":830,"Protein / Supplements":526,"Health":1820,"Grooming":50,"Travel":12380,"Maid":880,"Capital Replacement":0,"Child Experiences":0,"Home Refreshes/Interiors":0},"total":119397,"loggedAt":1782836277573},{"id":"log_zh4odkq","month":"2026-07","entries":{"Domestic Help (Cleaner+Maintenance)":9870,"Groceries":13984,"Cook":4500,"Nanny / Childcare":23000,"Insurance":2085,"Vape":8300,"Shopping":10867,"Gas Bill &amp; Utilities":675,"Vaccination":0,"Fuel &amp; Transport":9977,"Repairs":2600,"AI Project / Side projects":1840,"Baby Expenses":4797,"Eating Out / Movies":7689,"Gifts":2082,"Subscriptions (Netflix/Prime)":1477,"Protein / Supplements":804,"Health":1247,"Grooming":2120,"Travel":0,"Maid":3000,"Capital Replacement":8350,"Child Experiences":15046,"Home Refreshes/Interiors":0},"total":134310,"loggedAt":1787548574814},{"id":"log_h5v9azb","month":"2026-08","entries":{"Domestic Help (Cleaner+Maintenance)":18600,"Groceries":10598,"Cook":4500,"Nanny / Childcare":23000,"Insurance":2065,"Vape":9600,"Shopping":6400,"Gas Bill &amp; Utilities":389,"Vaccination":9120,"Fuel &amp; Transport":11723,"Repairs":2700,"AI Project / Side projects":10188,"Baby Expenses":11000,"Eating Out / Movies":7276,"Gifts":6741,"Subscriptions (Netflix/Prime)":1477,"Protein / Supplements":804,"Health":5804,"Grooming":1150,"Travel":900,"Maid":3000,"Capital Replacement":0,"Child Experiences":9390,"Home Refreshes/Interiors":6600},"total":163025,"loggedAt":1788359648795}],"profile":{"userName":"Kunal","spouseName":"Madhu","hasSpouse":true,"userAge":34,"spouseAge":35,"retirementAge":44,"lifeExpectancy":85,"children":[{"name":"Rahee","age":1}]},"inflation":{"general":0.08,"food":0.08,"education":0.1,"healthcare":0.12,"lifestyle":0.08},"returns":{"equity":0.12,"debt":0.07,"gold":0.08,"realestate":0.08,"epf":0.08,"cash":0.035},"risk":{"emergencyMonths":9,"healthReserve":500000,"bufferPct":0.05,"ltcReserve":1500000},"income":{"userMonthly":310000,"spouseMonthly":230000,"annualBonus":762000,"rsu":0,"otherIncome":0,"userGrowth":0.08,"spouseGrowth":0.08,"promotionJumpPct":0.15,"promotionEveryYears":4,"careerBreak":{"enabled":false,"startAge":36,"durationYears":1,"incomeReplacementPct":0}},"assets":[{"id":"a1","name":"Mutual Funds","owner":"Kunal","cls":"equity","balance":5832888,"monthlyContribution":86000,"stepUpPct":0.08},{"id":"a2","name":"Groww","owner":"Kunal","cls":"equity","balance":243498,"monthlyContribution":1500,"stepUpPct":0},{"id":"a3","name":"Amazon Stocks (RSU)","owner":"Kunal","cls":"equity","balance":2111263,"monthlyContribution":0,"stepUpPct":0},{"id":"a4","name":"EPFO","owner":"Kunal","cls":"epf","balance":1447167,"monthlyContribution":10800,"stepUpPct":0.08},{"id":"a5","name":"Savings","owner":"Kunal","cls":"cash","balance":160626,"monthlyContribution":0,"stepUpPct":0},{"id":"a6","name":"Fixed Deposit","owner":"Kunal","cls":"debt","balance":281593,"monthlyContribution":0,"stepUpPct":0},{"id":"a7","name":"ULIP","owner":"Kunal","cls":"debt","balance":99701,"monthlyContribution":10000,"stepUpPct":0},{"id":"a8","name":"US Stocks","owner":"Kunal","cls":"equity","balance":272792,"monthlyContribution":35000,"stepUpPct":0.08},{"id":"a9","name":"NPS","owner":"Kunal","cls":"epf","balance":319285,"monthlyContribution":5000,"stepUpPct":0},{"id":"a10","name":"Mutual Funds","owner":"Madhu","cls":"equity","balance":5795352,"monthlyContribution":119958,"stepUpPct":0.08},{"id":"a11","name":"Savings","owner":"Madhu","cls":"cash","balance":1094070,"monthlyContribution":0,"stepUpPct":0},{"id":"a12","name":"Fixed Deposit","owner":"Madhu","cls":"debt","balance":1081910,"monthlyContribution":0,"stepUpPct":0},{"id":"a13","name":"EPFO","owner":"Madhu","cls":"epf","balance":1743743,"monthlyContribution":10800,"stepUpPct":0.08},{"id":"a14","name":"Stocks","owner":"Madhu","cls":"equity","balance":399053,"monthlyContribution":11000,"stepUpPct":0},{"id":"a15","name":"NPS","owner":"Madhu","cls":"epf","balance":394323,"monthlyContribution":5000,"stepUpPct":0},{"id":"a16","name":"Gold","owner":"Madhu","cls":"gold","balance":153010,"monthlyContribution":0,"stepUpPct":0}],"liabilities":{"homeLoan":{"enabled":true,"principal":5300000,"rate":0.072,"tenureYears":24,"emi":38000},"personalLoan":{"enabled":false,"principal":0,"rate":0.12,"tenureYears":0,"emi":0},"vehicleLoan":{"enabled":false,"principal":0,"rate":0.09,"tenureYears":0,"emi":0},"otherDebt":{"enabled":false,"principal":0,"rate":0.1,"tenureYears":0,"emi":0},"prepayment":{"annualAmount":700000,"annualGrowthPct":0}},"expenses":[{"name":"Home Loan EMI","amount":38000,"group":"Survival","linkedToLoan":true,"inflationType":"general"},{"name":"Domestic Help (Cleaner+Maintenance)","amount":9600,"group":"Survival","inflationType":"general"},{"name":"Groceries","amount":14000,"group":"Survival","inflationType":"food","isBucket":true,"annualBudget":168000},{"name":"Cook","amount":4500,"group":"Survival","inflationType":"general"},{"name":"Nanny / Childcare","amount":23000,"group":"Survival","inflationType":"general"},{"name":"Insurance","amount":4000,"group":"Discretionary","inflationType":"general"},{"name":"Vape","amount":8000,"group":"Discretionary","inflationType":"lifestyle","isBucket":true,"annualBudget":96000},{"name":"Shopping","amount":9000,"group":"Discretionary","inflationType":"lifestyle","isBucket":true,"annualBudget":108000},{"name":"Gas Bill &amp; Utilities","amount":540,"group":"Survival","inflationType":"general"},{"name":"Vaccination","amount":3000,"group":"Survival","inflationType":"healthcare","isBucket":true,"annualBudget":36000},{"name":"Fuel &amp; Transport","amount":7000,"group":"Survival","inflationType":"general"},{"name":"Repairs","amount":5000,"group":"Survival","inflationType":"general","isBucket":true,"annualBudget":60000},{"name":"AI Project / Side projects","amount":3000,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Baby Expenses","amount":3000,"group":"Survival","inflationType":"healthcare"},{"name":"Eating Out / Movies","amount":8000,"group":"Discretionary","inflationType":"lifestyle","isBucket":true,"annualBudget":96000},{"name":"Gifts","amount":3000,"group":"Discretionary","inflationType":"lifestyle","isBucket":true,"annualBudget":36000},{"name":"Subscriptions (Netflix/Prime)","amount":1477,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Protein / Supplements","amount":1400,"group":"Survival","inflationType":"healthcare"},{"name":"Health","amount":1500,"group":"Survival","inflationType":"healthcare"},{"name":"Grooming","amount":4000,"group":"Survival","inflationType":"lifestyle","isBucket":true,"annualBudget":48000},{"name":"Travel","amount":30000,"group":"Discretionary","inflationType":"lifestyle","isBucket":true,"annualBudget":360000,"topUps":[{"id":"topup_t1874gn","amount":100000,"note":"Annual Performance Bonus","date":"2026-08-24"}]},{"name":"Maid","amount":3000,"group":"Survival"},{"name":"Capital Replacement","amount":10000,"group":"Survival","inflationType":"lifestyle","isBucket":true,"annualBudget":120000},{"name":"Child Experiences","amount":11000,"group":"Discretionary","inflationType":"lifestyle","isBucket":true,"annualBudget":132000},{"name":"Home Refreshes/Interiors","amount":5000,"group":"Discretionary","inflationType":"lifestyle","isBucket":true,"annualBudget":60000}],"goals":[{"id":"g1","type":"education","name":"Child 1 — Foreign Masters","childIndex":0,"targetAge":23,"costToday":7000000,"inflation":0.09},{"id":"g2","type":"marriage","name":"Child 1 — Marriage","childIndex":0,"targetAge":28,"costToday":2500000,"inflation":0.07},{"id":"g4","type":"car","name":"Car Replacement","recurring":true,"frequencyYears":7,"costToday":1200000,"inflation":0.06,"startYear":2029}],"fire":{"type":"comfortable","retirementSpendPct":1,"postRetMonthlySpendToday":136050,"swr":0.03,"sequence":"neutral","fatMultiplier":1.5},"scenarios":[{"id":"sc_z49l70n","name":"Retire at 45 at 3% SWR","snapshot":{"profile":{"userName":"Kunal","spouseName":"Madhu","hasSpouse":true,"userAge":34,"spouseAge":35,"retirementAge":45,"lifeExpectancy":85,"children":[{"name":"Child 1","age":1}]},"income":{"userMonthly":200000,"spouseMonthly":200000,"annualBonus":950000,"rsu":0,"otherIncome":0,"userGrowth":0.08,"spouseGrowth":0.08,"promotionJumpPct":0.15,"promotionEveryYears":4,"careerBreak":{"enabled":false,"startAge":36,"durationYears":1,"incomeReplacementPct":0}},"assets":[{"id":"a1","name":"Mutual Funds","owner":"Kunal","cls":"equity","balance":5424000,"monthlyContribution":90000,"stepUpPct":0.08},{"id":"a2","name":"Groww","owner":"Kunal","cls":"equity","balance":245454,"monthlyContribution":5000,"stepUpPct":0.08},{"id":"a3","name":"Amazon Stocks (RSU)","owner":"Kunal","cls":"equity","balance":1868996,"monthlyContribution":0,"stepUpPct":0},{"id":"a4","name":"EPFO","owner":"Kunal","cls":"epf","balance":1423493,"monthlyContribution":18000,"stepUpPct":0.08},{"id":"a5","name":"Savings","owner":"Kunal","cls":"cash","balance":83552,"monthlyContribution":0,"stepUpPct":0},{"id":"a6","name":"Fixed Deposit","owner":"Kunal","cls":"debt","balance":281593,"monthlyContribution":0,"stepUpPct":0},{"id":"a7","name":"ULIP","owner":"Kunal","cls":"debt","balance":77196,"monthlyContribution":2000,"stepUpPct":0},{"id":"a8","name":"US Stocks","owner":"Kunal","cls":"equity","balance":208176,"monthlyContribution":10000,"stepUpPct":0.08},{"id":"a9","name":"NPS","owner":"Kunal","cls":"epf","balance":298189,"monthlyContribution":5000,"stepUpPct":0.08},{"id":"a10","name":"Mutual Funds","owner":"Madhu","cls":"equity","balance":5336945,"monthlyContribution":110000,"stepUpPct":0.08},{"id":"a11","name":"Savings","owner":"Madhu","cls":"cash","balance":1193087,"monthlyContribution":0,"stepUpPct":0},{"id":"a12","name":"Fixed Deposit","owner":"Madhu","cls":"debt","balance":1083873,"monthlyContribution":0,"stepUpPct":0},{"id":"a13","name":"EPFO","owner":"Madhu","cls":"epf","balance":1743743,"monthlyContribution":16000,"stepUpPct":0.08},{"id":"a14","name":"Stocks","owner":"Madhu","cls":"equity","balance":368384,"monthlyContribution":5054.5,"stepUpPct":0.08},{"id":"a15","name":"NPS","owner":"Madhu","cls":"epf","balance":368690,"monthlyContribution":5000,"stepUpPct":0.08},{"id":"a16","name":"Gold","owner":"Madhu","cls":"gold","balance":155910,"monthlyContribution":0,"stepUpPct":0}],"liabilities":{"homeLoan":{"enabled":true,"principal":6000000,"rate":0.072,"tenureYears":25,"emi":38000},"personalLoan":{"enabled":false,"principal":0,"rate":0.12,"tenureYears":0,"emi":0},"vehicleLoan":{"enabled":false,"principal":0,"rate":0.09,"tenureYears":0,"emi":0},"otherDebt":{"enabled":false,"principal":0,"rate":0.1,"tenureYears":0,"emi":0},"prepayment":{"annualAmount":700000,"annualGrowthPct":0.08}},"expenses":[{"name":"Home Loan EMI","amount":38000,"group":"Survival","linkedToLoan":true,"inflationType":"general"},{"name":"Domestic Help (Cleaner+Maintenance)","amount":9700,"group":"Survival","inflationType":"general"},{"name":"Groceries","amount":13800,"group":"Survival","inflationType":"food"},{"name":"Cook","amount":3300,"group":"Survival","inflationType":"food"},{"name":"Nanny / Childcare","amount":16300,"group":"Survival","inflationType":"general"},{"name":"Insurance","amount":3600,"group":"Discretionary","inflationType":"general"},{"name":"Vape","amount":7050,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Shopping","amount":7580,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Gas Bill &amp; Utilities","amount":540,"group":"Survival","inflationType":"general"},{"name":"Vaccination","amount":2850,"group":"Survival","inflationType":"healthcare"},{"name":"Fuel &amp; Transport","amount":4980,"group":"Survival","inflationType":"general"},{"name":"Repairs","amount":3660,"group":"Survival","inflationType":"general"},{"name":"AI Project / Side projects","amount":2490,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Baby Expenses","amount":5670,"group":"Survival","inflationType":"healthcare"},{"name":"Eating Out / Movies","amount":7920,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Gifts","amount":2640,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Subscriptions (Netflix/Prime)","amount":830,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Protein / Supplements","amount":960,"group":"Survival","inflationType":"healthcare"},{"name":"Health","amount":1270,"group":"Survival","inflationType":"healthcare"},{"name":"Grooming","amount":3240,"group":"Survival","inflationType":"lifestyle"},{"name":"Travel","amount":15280,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Maid","amount":3000,"group":"Survival"},{"name":"Capital Replacement","amount":10000,"group":"Survival","inflationType":"lifestyle"},{"name":"Child Experiences","amount":5000,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Home Refreshes/Interiors","amount":5000,"group":"Discretionary","inflationType":"lifestyle"}],"goals":[{"id":"g1","type":"education","name":"Child 1 — Foreign Masters","childIndex":0,"targetAge":23,"costToday":7000000,"inflation":0.09},{"id":"g2","type":"marriage","name":"Child 1 — Marriage","childIndex":0,"targetAge":28,"costToday":2500000,"inflation":0.07},{"id":"g4","type":"car","name":"Car Replacement","recurring":true,"frequencyYears":7,"costToday":1200000,"inflation":0.06,"startYear":2029}],"fire":{"type":"comfortable","retirementSpendPct":1,"postRetMonthlySpendToday":136050,"swr":0.03,"sequence":"neutral","fatMultiplier":1.5},"returns":{"equity":0.12,"debt":0.07,"gold":0.08,"realestate":0.08,"epf":0.08,"cash":0.035},"inflation":{"general":0.07,"food":0.07,"education":0.1,"healthcare":0.12,"lifestyle":0.08},"risk":{"emergencyMonths":9,"healthReserve":500000,"bufferPct":0.05,"ltcReserve":1500000}},"createdAt":1782751893034},{"id":"sc_pzn9rzn","name":"Retire at 44 at 3% SWR","snapshot":{"profile":{"userName":"Kunal","spouseName":"Madhu","hasSpouse":true,"userAge":34,"spouseAge":35,"retirementAge":44,"lifeExpectancy":85,"children":[{"name":"Child 1","age":1}]},"income":{"userMonthly":200000,"spouseMonthly":200000,"annualBonus":950000,"rsu":0,"otherIncome":0,"userGrowth":0.08,"spouseGrowth":0.08,"promotionJumpPct":0.15,"promotionEveryYears":4,"careerBreak":{"enabled":false,"startAge":36,"durationYears":1,"incomeReplacementPct":0}},"assets":[{"id":"a1","name":"Mutual Funds","owner":"Kunal","cls":"equity","balance":5424000,"monthlyContribution":90000,"stepUpPct":0.08},{"id":"a2","name":"Groww","owner":"Kunal","cls":"equity","balance":245454,"monthlyContribution":5000,"stepUpPct":0.08},{"id":"a3","name":"Amazon Stocks (RSU)","owner":"Kunal","cls":"equity","balance":1868996,"monthlyContribution":0,"stepUpPct":0},{"id":"a4","name":"EPFO","owner":"Kunal","cls":"epf","balance":1423493,"monthlyContribution":18000,"stepUpPct":0.08},{"id":"a5","name":"Savings","owner":"Kunal","cls":"cash","balance":83552,"monthlyContribution":0,"stepUpPct":0},{"id":"a6","name":"Fixed Deposit","owner":"Kunal","cls":"debt","balance":281593,"monthlyContribution":0,"stepUpPct":0},{"id":"a7","name":"ULIP","owner":"Kunal","cls":"debt","balance":77196,"monthlyContribution":2000,"stepUpPct":0},{"id":"a8","name":"US Stocks","owner":"Kunal","cls":"equity","balance":208176,"monthlyContribution":10000,"stepUpPct":0.08},{"id":"a9","name":"NPS","owner":"Kunal","cls":"epf","balance":298189,"monthlyContribution":5000,"stepUpPct":0.08},{"id":"a10","name":"Mutual Funds","owner":"Madhu","cls":"equity","balance":5336945,"monthlyContribution":110000,"stepUpPct":0.08},{"id":"a11","name":"Savings","owner":"Madhu","cls":"cash","balance":1193087,"monthlyContribution":0,"stepUpPct":0},{"id":"a12","name":"Fixed Deposit","owner":"Madhu","cls":"debt","balance":1083873,"monthlyContribution":0,"stepUpPct":0},{"id":"a13","name":"EPFO","owner":"Madhu","cls":"epf","balance":1743743,"monthlyContribution":16000,"stepUpPct":0.08},{"id":"a14","name":"Stocks","owner":"Madhu","cls":"equity","balance":368384,"monthlyContribution":5054.5,"stepUpPct":0.08},{"id":"a15","name":"NPS","owner":"Madhu","cls":"epf","balance":368690,"monthlyContribution":5000,"stepUpPct":0.08},{"id":"a16","name":"Gold","owner":"Madhu","cls":"gold","balance":155910,"monthlyContribution":0,"stepUpPct":0}],"liabilities":{"homeLoan":{"enabled":true,"principal":6000000,"rate":0.072,"tenureYears":25,"emi":38000},"personalLoan":{"enabled":false,"principal":0,"rate":0.12,"tenureYears":0,"emi":0},"vehicleLoan":{"enabled":false,"principal":0,"rate":0.09,"tenureYears":0,"emi":0},"otherDebt":{"enabled":false,"principal":0,"rate":0.1,"tenureYears":0,"emi":0},"prepayment":{"annualAmount":700000,"annualGrowthPct":0.08}},"expenses":[{"name":"Home Loan EMI","amount":38000,"group":"Survival","linkedToLoan":true,"inflationType":"general"},{"name":"Domestic Help (Cleaner+Maintenance)","amount":9700,"group":"Survival","inflationType":"general"},{"name":"Groceries","amount":13800,"group":"Survival","inflationType":"food"},{"name":"Cook","amount":3300,"group":"Survival","inflationType":"food"},{"name":"Nanny / Childcare","amount":16300,"group":"Survival","inflationType":"general"},{"name":"Insurance","amount":3600,"group":"Discretionary","inflationType":"general"},{"name":"Vape","amount":7050,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Shopping","amount":7580,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Gas Bill &amp; Utilities","amount":540,"group":"Survival","inflationType":"general"},{"name":"Vaccination","amount":2850,"group":"Survival","inflationType":"healthcare"},{"name":"Fuel &amp; Transport","amount":4980,"group":"Survival","inflationType":"general"},{"name":"Repairs","amount":3660,"group":"Survival","inflationType":"general"},{"name":"AI Project / Side projects","amount":2490,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Baby Expenses","amount":5670,"group":"Survival","inflationType":"healthcare"},{"name":"Eating Out / Movies","amount":7920,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Gifts","amount":2640,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Subscriptions (Netflix/Prime)","amount":830,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Protein / Supplements","amount":960,"group":"Survival","inflationType":"healthcare"},{"name":"Health","amount":1270,"group":"Survival","inflationType":"healthcare"},{"name":"Grooming","amount":3240,"group":"Survival","inflationType":"lifestyle"},{"name":"Travel","amount":15280,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Maid","amount":3000,"group":"Survival"},{"name":"Capital Replacement","amount":10000,"group":"Survival","inflationType":"lifestyle"},{"name":"Child Experiences","amount":5000,"group":"Discretionary","inflationType":"lifestyle"},{"name":"Home Refreshes/Interiors","amount":5000,"group":"Discretionary","inflationType":"lifestyle"}],"goals":[{"id":"g1","type":"education","name":"Child 1 — Foreign Masters","childIndex":0,"targetAge":23,"costToday":7000000,"inflation":0.09},{"id":"g2","type":"marriage","name":"Child 1 — Marriage","childIndex":0,"targetAge":28,"costToday":2500000,"inflation":0.07},{"id":"g4","type":"car","name":"Car Replacement","recurring":true,"frequencyYears":7,"costToday":1200000,"inflation":0.06,"startYear":2029}],"fire":{"type":"comfortable","retirementSpendPct":1,"postRetMonthlySpendToday":136050,"swr":0.03,"sequence":"neutral","fatMultiplier":1.5},"returns":{"equity":0.12,"debt":0.07,"gold":0.08,"realestate":0.08,"epf":0.08,"cash":0.035},"inflation":{"general":0.07,"food":0.07,"education":0.1,"healthcare":0.12,"lifestyle":0.08},"risk":{"emergencyMonths":9,"healthReserve":500000,"bufferPct":0.05,"ltcReserve":1500000}},"createdAt":1782751922830}],"badges":{}}</v>
       </c>
     </row>
   </sheetData>
